--- a/public/modelos/biblioteca-v2/PCM-MAN-001_Controle-Documental_R00.xlsx
+++ b/public/modelos/biblioteca-v2/PCM-MAN-001_Controle-Documental_R00.xlsx
@@ -10,22 +10,33 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisões de documentos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cadastros" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisões" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organização" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referências" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cadastros" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisões" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="L_PESSOAS">tb_pcm_pessoas[nome_pessoa]</definedName>
     <definedName name="L_TIPO_DOC">tb_pcm_tipos_documento[tipo_documento]</definedName>
     <definedName name="L_STATUS_DOC">tb_pcm_status_documento[status_documento]</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Leia-me'!$A$1:$G$31</definedName>
+    <definedName name="L_SIT_REF">tb_pcm_situacoes_referencia[situacao_referencia]</definedName>
+    <definedName name="L_SIM_NAO">tb_pcm_sim_nao[sim_nao]</definedName>
+    <definedName name="organizacao">'Organização'!$A$4</definedName>
+    <definedName name="referencial">'Organização'!$A$6</definedName>
+    <definedName name="meta_disponibilidade">'Organização'!$A$8</definedName>
+    <definedName name="meta_aderencia">'Organização'!$D$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Leia-me'!$A$1:$G$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Documentos'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Documentos'!$A$1:$J$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revisões de documentos'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revisões de documentos'!$A$1:$F$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cadastros'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cadastros'!$A$1:$C$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Revisões'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Revisões'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Organização'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Referências'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Referências'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cadastros'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cadastros'!$A$1:$D$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Revisões'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Revisões'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,10 +44,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,15 +94,32 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial Black"/>
-      <color rgb="000B2A5B"/>
-      <sz val="16"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B7686"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E1726"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="006B7686"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial Black"/>
+      <color rgb="000E1726"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial Black"/>
+      <color rgb="000B2A5B"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -119,12 +148,6 @@
       <b val="1"/>
       <color rgb="000E1726"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006B7686"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -204,7 +227,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -365,11 +388,190 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="000B2A5B"/>
+        <color rgb="00D3DEEC"/>
+      </left>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3DEEC"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3DEEC"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3DEEC"/>
       </left>
       <right style="thin">
-        <color rgb="000B2A5B"/>
+        <color rgb="00D3DEEC"/>
       </right>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3DEEC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3DEEC"/>
+      </left>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3DEEC"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3DEEC"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="00D3DEEC"/>
       </bottom>
@@ -439,25 +641,6 @@
       </bottom>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00D3DEEC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D3DEEC"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="00D3DEEC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D3DEEC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D3DEEC"/>
-      </bottom>
-    </border>
-    <border>
       <bottom style="thin">
         <color rgb="00FFFFFF"/>
       </bottom>
@@ -471,9 +654,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -482,73 +665,73 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="5" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -558,22 +741,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -654,22 +837,71 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -682,10 +914,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="00B3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FDECEA"/>
+          <bgColor rgb="00FDECEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="00B3261E"/>
       </font>
       <fill>
@@ -876,7 +1119,27 @@
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>Responsável.</t>
+        <t>Referência.</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Versão.</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Data. Data no formato dd/mm/aaaa. Exemplo: 30/10/2026.</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>Fonte (link ou local).</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Situação. Escolha na lista: Verificada, Não verificada.</t>
       </text>
     </comment>
   </commentList>
@@ -884,6 +1147,36 @@
 </file>
 
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>PCM Direto</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>Responsável.</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Função.</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Especialidade.</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>Ativo. Escolha na lista: Sim, Não.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>PCM Direto</author>
@@ -949,7 +1242,7 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>29</row>
+      <row>32</row>
       <rowOff>104775</rowOff>
     </from>
     <ext cx="1609725" cy="476250"/>
@@ -1038,11 +1331,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>266700</colOff>
+      <colOff>76200</colOff>
       <row>0</row>
-      <rowOff>47625</rowOff>
+      <rowOff>190500</rowOff>
     </from>
-    <ext cx="2162175" cy="647700"/>
+    <ext cx="1809750" cy="542925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1064,6 +1357,66 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>542925</colOff>
+      <row>0</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2209800" cy="666750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>504825</colOff>
+      <row>0</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2209800" cy="666750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1116,7 +1469,27 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_pcm_documentos" displayName="tb_pcm_documentos" ref="A4:J29" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_pcm_situacoes_referencia" displayName="tb_pcm_situacoes_referencia" ref="O11:O13" headerRowCount="1">
+  <autoFilter ref="O11:O13"/>
+  <tableColumns count="1">
+    <tableColumn id="15" name="situacao_referencia"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tb_pcm_sim_nao" displayName="tb_pcm_sim_nao" ref="Q11:Q13" headerRowCount="1">
+  <autoFilter ref="Q11:Q13"/>
+  <tableColumns count="1">
+    <tableColumn id="17" name="sim_nao"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tb_pcm_documentos" displayName="tb_pcm_documentos" ref="A4:J29" headerRowCount="1">
   <autoFilter ref="A4:J29"/>
   <tableColumns count="10">
     <tableColumn id="1" name="codigo_documento"/>
@@ -1134,8 +1507,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tb_pcm_revisoes" displayName="tb_pcm_revisoes" ref="A4:F29" headerRowCount="1">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tb_pcm_revisoes" displayName="tb_pcm_revisoes" ref="A4:F29" headerRowCount="1">
   <autoFilter ref="A4:F29"/>
   <tableColumns count="6">
     <tableColumn id="1" name="codigo_documento"/>
@@ -1149,18 +1522,35 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tb_pcm_pessoas" displayName="tb_pcm_pessoas" ref="A4:A29" headerRowCount="1">
-  <autoFilter ref="A4:A29"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="nome_pessoa"/>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tb_pcm_referencias" displayName="tb_pcm_referencias" ref="A4:E29" headerRowCount="1">
+  <autoFilter ref="A4:E29"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="referencia"/>
+    <tableColumn id="2" name="versao"/>
+    <tableColumn id="3" name="data"/>
+    <tableColumn id="4" name="fonte"/>
+    <tableColumn id="5" name="situacao"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tb_pcm_revisoes_modelo" displayName="tb_pcm_revisoes_modelo" ref="A4:E29" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tb_pcm_pessoas" displayName="tb_pcm_pessoas" ref="A4:D29" headerRowCount="1">
+  <autoFilter ref="A4:D29"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="nome_pessoa"/>
+    <tableColumn id="2" name="funcao"/>
+    <tableColumn id="3" name="especialidade"/>
+    <tableColumn id="4" name="ativo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tb_pcm_revisoes_modelo" displayName="tb_pcm_revisoes_modelo" ref="A4:E29" headerRowCount="1">
   <autoFilter ref="A4:E29"/>
   <tableColumns count="5">
     <tableColumn id="1" name="revisao"/>
@@ -1463,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M31"/>
+  <dimension ref="B1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1479,6 +1869,10 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="2" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="2" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1673,6 +2067,10 @@
       <c r="K9" s="18" t="n"/>
       <c r="L9" s="18" t="n"/>
       <c r="M9" s="18" t="n"/>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="18" t="n"/>
+      <c r="P9" s="18" t="n"/>
+      <c r="Q9" s="18" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="B10" s="19" t="inlineStr">
@@ -1710,6 +2108,16 @@
       <c r="M10" s="24" t="inlineStr">
         <is>
           <t>Significado</t>
+        </is>
+      </c>
+      <c r="O10" s="24" t="inlineStr">
+        <is>
+          <t>Situação da referência</t>
+        </is>
+      </c>
+      <c r="Q10" s="24" t="inlineStr">
+        <is>
+          <t>Sim ou não</t>
         </is>
       </c>
     </row>
@@ -1747,6 +2155,16 @@
           <t>rotulo_status</t>
         </is>
       </c>
+      <c r="O11" s="26" t="inlineStr">
+        <is>
+          <t>situacao_referencia</t>
+        </is>
+      </c>
+      <c r="Q11" s="26" t="inlineStr">
+        <is>
+          <t>sim_nao</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
@@ -1780,6 +2198,16 @@
       <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Rascunho</t>
+        </is>
+      </c>
+      <c r="O12" s="27" t="inlineStr">
+        <is>
+          <t>Verificada</t>
+        </is>
+      </c>
+      <c r="Q12" s="27" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -1815,6 +2243,16 @@
       <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Vigente</t>
+        </is>
+      </c>
+      <c r="O13" s="27" t="inlineStr">
+        <is>
+          <t>Não verificada</t>
+        </is>
+      </c>
+      <c r="Q13" s="27" t="inlineStr">
+        <is>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -2008,9 +2446,60 @@
       <c r="E21" s="34" t="n"/>
       <c r="F21" s="34" t="n"/>
     </row>
-    <row r="22" ht="10" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="34" customHeight="1">
+      <c r="B22" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>Organização</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Digite o nome da empresa, o referencial usado (deixe "GERAL (sem norma)" se não houver) e as metas de disponibilidade e aderência, de 0 a 100.</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="B23" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>Referências</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Liste as normas e os manuais de fabricante que a manutenção usa, com versão, data e onde encontrar. Marque Verificada só depois de conferir; sem versão, data ou fonte, a linha fica em vermelho.</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="34" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="B24" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Cadastros</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Na lista de pessoas, informe também a função, a especialidade e se a pessoa está ativa (Sim ou Não).</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="34" t="n"/>
+    </row>
+    <row r="25" ht="10" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2030,163 +2519,169 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>▼  Lista</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="n"/>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Clique na célula e escolha na seta. Valor fora da lista é recusado.</t>
-        </is>
-      </c>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="34" t="n"/>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>Célula branca</t>
-        </is>
-      </c>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Campo para digitar.</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n"/>
-      <c r="F25" s="34" t="n"/>
-    </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>Célula cinza</t>
-        </is>
-      </c>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="33" t="inlineStr">
-        <is>
-          <t>Cálculo automático. Não digite: a fórmula preenche sozinha.</t>
-        </is>
-      </c>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="34" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="B27" s="35" t="inlineStr">
         <is>
-          <t>Datas e números</t>
+          <t>▼  Lista</t>
         </is>
       </c>
       <c r="C27" s="34" t="n"/>
       <c r="D27" s="33" t="inlineStr">
         <is>
-          <t>Datas em dd/mm/aaaa; decimais com vírgula. Vazio = sem informação; zero é valor real.</t>
+          <t>Clique na célula e escolha na seta. Valor fora da lista é recusado.</t>
         </is>
       </c>
       <c r="E27" s="34" t="n"/>
       <c r="F27" s="34" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="35" t="inlineStr">
-        <is>
-          <t>Impressão</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="n"/>
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>Célula branca</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n"/>
       <c r="D28" s="33" t="inlineStr">
         <is>
-          <t>Cada aba já está ajustada para uma folha A4. Use Arquivo &gt; Imprimir sem mudar a escala.</t>
+          <t>Campo para digitar.</t>
         </is>
       </c>
       <c r="E28" s="34" t="n"/>
       <c r="F28" s="34" t="n"/>
     </row>
-    <row r="29" ht="12" customHeight="1"/>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="39" t="n"/>
-      <c r="C30" s="39" t="n"/>
-      <c r="D30" s="40" t="inlineStr">
+    <row r="29" ht="21" customHeight="1">
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>Célula cinza</t>
+        </is>
+      </c>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Cálculo automático. Não digite: a fórmula preenche sozinha.</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="34" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>Datas e números</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>Datas em dd/mm/aaaa; decimais com vírgula. Vazio = sem informação; zero é valor real.</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="34" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>Impressão</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n"/>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>Cada aba já está ajustada para uma folha A4. Use Arquivo &gt; Imprimir sem mudar a escala.</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="34" t="n"/>
+    </row>
+    <row r="32" ht="12" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="39" t="n"/>
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="40" t="inlineStr">
         <is>
           <t>SOBRE O PCM DIRETO</t>
         </is>
       </c>
-      <c r="E30" s="39" t="n"/>
-      <c r="F30" s="41" t="inlineStr">
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="41" t="inlineStr">
         <is>
           <t>pcmdireto.me</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="B31" s="42" t="n"/>
-      <c r="C31" s="42" t="n"/>
-      <c r="D31" s="43" t="inlineStr">
+    <row r="34" ht="34" customHeight="1">
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="43" t="inlineStr">
         <is>
           <t>Modelos de manutenção prontos para usar, do planejamento ao controle: criticidade, plano, ordem de serviço, indicadores e auditorias. Todos no mesmo padrão, para a equipe aprender uma vez e usar em todos.</t>
         </is>
       </c>
-      <c r="E31" s="42" t="n"/>
-      <c r="F31" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="I9:M9"/>
+  <mergeCells count="44">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D27:F27"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B33:C34"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="B1:C3"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D23:F23"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="I9:Q9"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D33:E33"/>
     <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D22:F22"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink ref="C19" location="'Cadastros'!A1" display="Cadastros"/>
     <hyperlink ref="C20" location="'Documentos'!A1" display="Documentos"/>
     <hyperlink ref="C21" location="'Revisões de documentos'!A1" display="Revisões de documentos"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId2"/>
+    <hyperlink ref="C22" location="'Organização'!A1" display="Organização"/>
+    <hyperlink ref="C23" location="'Referências'!A1" display="Referências"/>
+    <hyperlink ref="C24" location="'Cadastros'!A1" display="Cadastros"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId2"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.6" header="0.5" footer="0.25"/>
@@ -2200,9 +2695,11 @@
     <firstFooter/>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  <tableParts count="2">
+  <tableParts count="4">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3112,126 +3609,459 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30.75" customHeight="1">
+      <c r="A1" s="44" t="n"/>
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="76" t="inlineStr">
+        <is>
+          <t>Organização</t>
+        </is>
+      </c>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="48">
+        <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
+        <v/>
+      </c>
+      <c r="F1" s="45" t="n"/>
+    </row>
+    <row r="2" ht="42.5" customHeight="1">
+      <c r="A2" s="49" t="n"/>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="51" t="inlineStr">
+        <is>
+          <t>Objetivo: Nome da empresa, referencial adotado e metas de disponibilidade e aderência</t>
+        </is>
+      </c>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="51">
+        <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
+        <v/>
+      </c>
+      <c r="F2" s="50" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="77" t="inlineStr">
+        <is>
+          <t>Organização (nome da empresa)</t>
+        </is>
+      </c>
+      <c r="B3" s="78" t="n"/>
+      <c r="C3" s="78" t="n"/>
+      <c r="D3" s="78" t="n"/>
+      <c r="E3" s="78" t="n"/>
+      <c r="F3" s="79" t="n"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="80" t="n"/>
+      <c r="B4" s="22" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="22" t="n"/>
+      <c r="F4" s="81" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Referencial (norma ou referência usada)</t>
+        </is>
+      </c>
+      <c r="F5" s="83" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>GERAL (sem norma)</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="81" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="84" t="inlineStr">
+        <is>
+          <t>Meta de disponibilidade (%)</t>
+        </is>
+      </c>
+      <c r="D7" s="85" t="inlineStr">
+        <is>
+          <t>Meta de aderência (%)</t>
+        </is>
+      </c>
+      <c r="F7" s="83" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="86" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="81" t="n"/>
+      <c r="D8" s="86" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="81" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="87" t="n"/>
+      <c r="B9" s="88" t="n"/>
+      <c r="C9" s="88" t="n"/>
+      <c r="D9" s="88" t="n"/>
+      <c r="E9" s="88" t="n"/>
+      <c r="F9" s="89" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="90" t="inlineStr">
+        <is>
+          <t>Digite as metas de 0 a 100. Elas alimentam os indicadores do PCM Direto. Referencial: deixe "GERAL (sem norma)" se a empresa não segue uma norma.</t>
+        </is>
+      </c>
+      <c r="B10" s="91" t="n"/>
+      <c r="C10" s="91" t="n"/>
+      <c r="D10" s="91" t="n"/>
+      <c r="E10" s="91" t="n"/>
+      <c r="F10" s="92" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="93" t="n"/>
+      <c r="B11" s="93" t="n"/>
+      <c r="C11" s="93" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="93" t="n"/>
+      <c r="B12" s="93" t="n"/>
+      <c r="C12" s="93" t="n"/>
+      <c r="D12" s="93" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A7:C7"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="A8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Número inválido" error="Digite um número de 0 a 100." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Número inválido" error="Digite um número de 0 a 100." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.2" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;7 &amp;K4A5668PCM-MAN-001  ·  Manutenção planejada. Direto ao ponto.&amp;C&amp;7 &amp;K4A5668Página &amp;P de &amp;N&amp;R&amp;7 &amp;K4A5668PCM Direto  ·  Impresso em &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F5AA6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="19.8" customWidth="1" min="2" max="2"/>
+    <col width="21.3" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="25.7" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
       <c r="A1" s="72" t="n"/>
-      <c r="B1" s="76" t="inlineStr">
-        <is>
-          <t>Cadastros</t>
-        </is>
-      </c>
-      <c r="C1" s="77">
+      <c r="B1" s="46" t="inlineStr">
+        <is>
+          <t>Referências</t>
+        </is>
+      </c>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="94">
         <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
         <v/>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="31" customHeight="1">
       <c r="A2" s="73" t="n"/>
-      <c r="B2" s="78" t="inlineStr">
-        <is>
-          <t>Objetivo: Cadastre aqui os itens usados nas listas (▼) das outras abas.</t>
-        </is>
-      </c>
-      <c r="C2" s="78">
+      <c r="B2" s="51" t="inlineStr">
+        <is>
+          <t>Objetivo: Normas e manuais de fabricante usados na manutenção: versão, data, fonte e situação da conferência</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="95">
         <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="79" t="inlineStr">
-        <is>
-          <t>Responsável</t>
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>Referência</t>
+        </is>
+      </c>
+      <c r="B3" s="54" t="inlineStr">
+        <is>
+          <t>Versão</t>
+        </is>
+      </c>
+      <c r="C3" s="54" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D3" s="54" t="inlineStr">
+        <is>
+          <t>Fonte (link ou local)</t>
+        </is>
+      </c>
+      <c r="E3" s="55" t="inlineStr">
+        <is>
+          <t>Situação ▼</t>
         </is>
       </c>
     </row>
     <row r="4" hidden="1">
       <c r="A4" s="56" t="inlineStr">
         <is>
-          <t>nome_pessoa</t>
+          <t>referencia</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="E4" s="56" t="inlineStr">
+        <is>
+          <t>situacao</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="80" t="n"/>
+      <c r="A5" s="96" t="n"/>
+      <c r="B5" s="97" t="n"/>
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="58" t="n"/>
+      <c r="E5" s="98" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="80" t="n"/>
+      <c r="A6" s="96" t="n"/>
+      <c r="B6" s="97" t="n"/>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="58" t="n"/>
+      <c r="E6" s="98" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="80" t="n"/>
+      <c r="A7" s="96" t="n"/>
+      <c r="B7" s="97" t="n"/>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="58" t="n"/>
+      <c r="E7" s="98" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="80" t="n"/>
+      <c r="A8" s="96" t="n"/>
+      <c r="B8" s="97" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="58" t="n"/>
+      <c r="E8" s="98" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="80" t="n"/>
+      <c r="A9" s="96" t="n"/>
+      <c r="B9" s="97" t="n"/>
+      <c r="C9" s="61" t="n"/>
+      <c r="D9" s="58" t="n"/>
+      <c r="E9" s="98" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="80" t="n"/>
+      <c r="A10" s="96" t="n"/>
+      <c r="B10" s="97" t="n"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="58" t="n"/>
+      <c r="E10" s="98" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="80" t="n"/>
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="97" t="n"/>
+      <c r="C11" s="61" t="n"/>
+      <c r="D11" s="58" t="n"/>
+      <c r="E11" s="98" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="80" t="n"/>
+      <c r="A12" s="96" t="n"/>
+      <c r="B12" s="97" t="n"/>
+      <c r="C12" s="61" t="n"/>
+      <c r="D12" s="58" t="n"/>
+      <c r="E12" s="98" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="80" t="n"/>
+      <c r="A13" s="96" t="n"/>
+      <c r="B13" s="97" t="n"/>
+      <c r="C13" s="61" t="n"/>
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="98" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="80" t="n"/>
+      <c r="A14" s="96" t="n"/>
+      <c r="B14" s="97" t="n"/>
+      <c r="C14" s="61" t="n"/>
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="98" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="80" t="n"/>
+      <c r="A15" s="96" t="n"/>
+      <c r="B15" s="97" t="n"/>
+      <c r="C15" s="61" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="98" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="80" t="n"/>
+      <c r="A16" s="96" t="n"/>
+      <c r="B16" s="97" t="n"/>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="98" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="80" t="n"/>
+      <c r="A17" s="96" t="n"/>
+      <c r="B17" s="97" t="n"/>
+      <c r="C17" s="61" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="98" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="80" t="n"/>
+      <c r="A18" s="96" t="n"/>
+      <c r="B18" s="97" t="n"/>
+      <c r="C18" s="61" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="98" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="80" t="n"/>
+      <c r="A19" s="96" t="n"/>
+      <c r="B19" s="97" t="n"/>
+      <c r="C19" s="61" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="98" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="80" t="n"/>
+      <c r="A20" s="96" t="n"/>
+      <c r="B20" s="97" t="n"/>
+      <c r="C20" s="61" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="98" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="80" t="n"/>
+      <c r="A21" s="96" t="n"/>
+      <c r="B21" s="97" t="n"/>
+      <c r="C21" s="61" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="98" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="80" t="n"/>
+      <c r="A22" s="96" t="n"/>
+      <c r="B22" s="97" t="n"/>
+      <c r="C22" s="61" t="n"/>
+      <c r="D22" s="58" t="n"/>
+      <c r="E22" s="98" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="80" t="n"/>
+      <c r="A23" s="96" t="n"/>
+      <c r="B23" s="97" t="n"/>
+      <c r="C23" s="61" t="n"/>
+      <c r="D23" s="58" t="n"/>
+      <c r="E23" s="98" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="80" t="n"/>
+      <c r="A24" s="96" t="n"/>
+      <c r="B24" s="97" t="n"/>
+      <c r="C24" s="61" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="98" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="80" t="n"/>
+      <c r="A25" s="96" t="n"/>
+      <c r="B25" s="97" t="n"/>
+      <c r="C25" s="61" t="n"/>
+      <c r="D25" s="58" t="n"/>
+      <c r="E25" s="98" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="80" t="n"/>
+      <c r="A26" s="96" t="n"/>
+      <c r="B26" s="97" t="n"/>
+      <c r="C26" s="61" t="n"/>
+      <c r="D26" s="58" t="n"/>
+      <c r="E26" s="98" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="80" t="n"/>
+      <c r="A27" s="96" t="n"/>
+      <c r="B27" s="97" t="n"/>
+      <c r="C27" s="61" t="n"/>
+      <c r="D27" s="58" t="n"/>
+      <c r="E27" s="98" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="80" t="n"/>
+      <c r="A28" s="96" t="n"/>
+      <c r="B28" s="97" t="n"/>
+      <c r="C28" s="61" t="n"/>
+      <c r="D28" s="58" t="n"/>
+      <c r="E28" s="98" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="81" t="n"/>
+      <c r="A29" s="99" t="n"/>
+      <c r="B29" s="100" t="n"/>
+      <c r="C29" s="68" t="n"/>
+      <c r="D29" s="65" t="n"/>
+      <c r="E29" s="101" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="71" t="inlineStr">
@@ -3242,13 +4072,27 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="C1"/>
-    <mergeCell ref="B2"/>
-    <mergeCell ref="C2"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1"/>
+    <mergeCell ref="E2"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:E29">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>AND($E5="Verificada",OR($B5="",$C5="",$D5=""))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Data inválida" error="Digite uma data válida (dd/mm/aaaa)." type="date" errorStyle="stop" operator="between">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="E5:E29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
+      <formula1>L_SIT_REF</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.2" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3268,7 +4112,283 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F5AA6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="47.9" customWidth="1" min="1" max="1"/>
+    <col width="47.9" customWidth="1" min="2" max="2"/>
+    <col width="47.9" customWidth="1" min="3" max="3"/>
+    <col width="21.2" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30.75" customHeight="1">
+      <c r="A1" s="72" t="n"/>
+      <c r="B1" s="102" t="inlineStr">
+        <is>
+          <t>Cadastros</t>
+        </is>
+      </c>
+      <c r="C1" s="48">
+        <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
+        <v/>
+      </c>
+      <c r="D1" s="45" t="n"/>
+    </row>
+    <row r="2" ht="31" customHeight="1">
+      <c r="A2" s="73" t="n"/>
+      <c r="B2" s="95" t="inlineStr">
+        <is>
+          <t>Objetivo: Cadastre aqui os itens usados nas listas (▼) das outras abas.</t>
+        </is>
+      </c>
+      <c r="C2" s="51">
+        <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
+        <v/>
+      </c>
+      <c r="D2" s="50" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="B3" s="54" t="inlineStr">
+        <is>
+          <t>Função</t>
+        </is>
+      </c>
+      <c r="C3" s="54" t="inlineStr">
+        <is>
+          <t>Especialidade</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>Ativo ▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t>nome_pessoa</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>funcao</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>especialidade</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>ativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="103" t="n"/>
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="60" t="n"/>
+      <c r="D5" s="98" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="103" t="n"/>
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="60" t="n"/>
+      <c r="D6" s="98" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="103" t="n"/>
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="60" t="n"/>
+      <c r="D7" s="98" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="103" t="n"/>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="98" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="103" t="n"/>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="60" t="n"/>
+      <c r="D9" s="98" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="103" t="n"/>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="98" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="103" t="n"/>
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="60" t="n"/>
+      <c r="D11" s="98" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="103" t="n"/>
+      <c r="B12" s="60" t="n"/>
+      <c r="C12" s="60" t="n"/>
+      <c r="D12" s="98" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="103" t="n"/>
+      <c r="B13" s="60" t="n"/>
+      <c r="C13" s="60" t="n"/>
+      <c r="D13" s="98" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="103" t="n"/>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="98" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="103" t="n"/>
+      <c r="B15" s="60" t="n"/>
+      <c r="C15" s="60" t="n"/>
+      <c r="D15" s="98" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="103" t="n"/>
+      <c r="B16" s="60" t="n"/>
+      <c r="C16" s="60" t="n"/>
+      <c r="D16" s="98" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="103" t="n"/>
+      <c r="B17" s="60" t="n"/>
+      <c r="C17" s="60" t="n"/>
+      <c r="D17" s="98" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="103" t="n"/>
+      <c r="B18" s="60" t="n"/>
+      <c r="C18" s="60" t="n"/>
+      <c r="D18" s="98" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="103" t="n"/>
+      <c r="B19" s="60" t="n"/>
+      <c r="C19" s="60" t="n"/>
+      <c r="D19" s="98" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="103" t="n"/>
+      <c r="B20" s="60" t="n"/>
+      <c r="C20" s="60" t="n"/>
+      <c r="D20" s="98" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="103" t="n"/>
+      <c r="B21" s="60" t="n"/>
+      <c r="C21" s="60" t="n"/>
+      <c r="D21" s="98" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="103" t="n"/>
+      <c r="B22" s="60" t="n"/>
+      <c r="C22" s="60" t="n"/>
+      <c r="D22" s="98" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="103" t="n"/>
+      <c r="B23" s="60" t="n"/>
+      <c r="C23" s="60" t="n"/>
+      <c r="D23" s="98" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="103" t="n"/>
+      <c r="B24" s="60" t="n"/>
+      <c r="C24" s="60" t="n"/>
+      <c r="D24" s="98" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="103" t="n"/>
+      <c r="B25" s="60" t="n"/>
+      <c r="C25" s="60" t="n"/>
+      <c r="D25" s="98" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="103" t="n"/>
+      <c r="B26" s="60" t="n"/>
+      <c r="C26" s="60" t="n"/>
+      <c r="D26" s="98" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="103" t="n"/>
+      <c r="B27" s="60" t="n"/>
+      <c r="C27" s="60" t="n"/>
+      <c r="D27" s="98" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="103" t="n"/>
+      <c r="B28" s="60" t="n"/>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="98" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="104" t="n"/>
+      <c r="B29" s="67" t="n"/>
+      <c r="C29" s="67" t="n"/>
+      <c r="D29" s="101" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
+      <formula1>L_SIM_NAO</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.2" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;7 &amp;K4A5668PCM-MAN-001  ·  Manutenção planejada. Direto ao ponto.&amp;C&amp;7 &amp;K4A5668Página &amp;P de &amp;N&amp;R&amp;7 &amp;K4A5668PCM Direto  ·  Impresso em &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -3288,7 +4408,7 @@
     <row r="1" ht="30.75" customHeight="1">
       <c r="A1" s="44" t="n"/>
       <c r="B1" s="45" t="n"/>
-      <c r="C1" s="76" t="inlineStr">
+      <c r="C1" s="102" t="inlineStr">
         <is>
           <t>Revisões</t>
         </is>
@@ -3302,7 +4422,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="49" t="n"/>
       <c r="B2" s="50" t="n"/>
-      <c r="C2" s="78" t="inlineStr">
+      <c r="C2" s="95" t="inlineStr">
         <is>
           <t>Objetivo: Registre cada alteração do modelo; a última linha alimenta Rev. e data do cabeçalho.</t>
         </is>
@@ -3368,7 +4488,7 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="82" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>00</t>
         </is>
@@ -3385,168 +4505,168 @@
       <c r="E5" s="74" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="82" t="n"/>
+      <c r="A6" s="105" t="n"/>
       <c r="B6" s="61" t="n"/>
       <c r="C6" s="58" t="n"/>
       <c r="D6" s="60" t="n"/>
       <c r="E6" s="74" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="82" t="n"/>
+      <c r="A7" s="105" t="n"/>
       <c r="B7" s="61" t="n"/>
       <c r="C7" s="58" t="n"/>
       <c r="D7" s="60" t="n"/>
       <c r="E7" s="74" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="82" t="n"/>
+      <c r="A8" s="105" t="n"/>
       <c r="B8" s="61" t="n"/>
       <c r="C8" s="58" t="n"/>
       <c r="D8" s="60" t="n"/>
       <c r="E8" s="74" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="82" t="n"/>
+      <c r="A9" s="105" t="n"/>
       <c r="B9" s="61" t="n"/>
       <c r="C9" s="58" t="n"/>
       <c r="D9" s="60" t="n"/>
       <c r="E9" s="74" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="82" t="n"/>
+      <c r="A10" s="105" t="n"/>
       <c r="B10" s="61" t="n"/>
       <c r="C10" s="58" t="n"/>
       <c r="D10" s="60" t="n"/>
       <c r="E10" s="74" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="82" t="n"/>
+      <c r="A11" s="105" t="n"/>
       <c r="B11" s="61" t="n"/>
       <c r="C11" s="58" t="n"/>
       <c r="D11" s="60" t="n"/>
       <c r="E11" s="74" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="82" t="n"/>
+      <c r="A12" s="105" t="n"/>
       <c r="B12" s="61" t="n"/>
       <c r="C12" s="58" t="n"/>
       <c r="D12" s="60" t="n"/>
       <c r="E12" s="74" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="82" t="n"/>
+      <c r="A13" s="105" t="n"/>
       <c r="B13" s="61" t="n"/>
       <c r="C13" s="58" t="n"/>
       <c r="D13" s="60" t="n"/>
       <c r="E13" s="74" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="82" t="n"/>
+      <c r="A14" s="105" t="n"/>
       <c r="B14" s="61" t="n"/>
       <c r="C14" s="58" t="n"/>
       <c r="D14" s="60" t="n"/>
       <c r="E14" s="74" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="82" t="n"/>
+      <c r="A15" s="105" t="n"/>
       <c r="B15" s="61" t="n"/>
       <c r="C15" s="58" t="n"/>
       <c r="D15" s="60" t="n"/>
       <c r="E15" s="74" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="82" t="n"/>
+      <c r="A16" s="105" t="n"/>
       <c r="B16" s="61" t="n"/>
       <c r="C16" s="58" t="n"/>
       <c r="D16" s="60" t="n"/>
       <c r="E16" s="74" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="82" t="n"/>
+      <c r="A17" s="105" t="n"/>
       <c r="B17" s="61" t="n"/>
       <c r="C17" s="58" t="n"/>
       <c r="D17" s="60" t="n"/>
       <c r="E17" s="74" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="82" t="n"/>
+      <c r="A18" s="105" t="n"/>
       <c r="B18" s="61" t="n"/>
       <c r="C18" s="58" t="n"/>
       <c r="D18" s="60" t="n"/>
       <c r="E18" s="74" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="82" t="n"/>
+      <c r="A19" s="105" t="n"/>
       <c r="B19" s="61" t="n"/>
       <c r="C19" s="58" t="n"/>
       <c r="D19" s="60" t="n"/>
       <c r="E19" s="74" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="82" t="n"/>
+      <c r="A20" s="105" t="n"/>
       <c r="B20" s="61" t="n"/>
       <c r="C20" s="58" t="n"/>
       <c r="D20" s="60" t="n"/>
       <c r="E20" s="74" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="82" t="n"/>
+      <c r="A21" s="105" t="n"/>
       <c r="B21" s="61" t="n"/>
       <c r="C21" s="58" t="n"/>
       <c r="D21" s="60" t="n"/>
       <c r="E21" s="74" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="82" t="n"/>
+      <c r="A22" s="105" t="n"/>
       <c r="B22" s="61" t="n"/>
       <c r="C22" s="58" t="n"/>
       <c r="D22" s="60" t="n"/>
       <c r="E22" s="74" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="82" t="n"/>
+      <c r="A23" s="105" t="n"/>
       <c r="B23" s="61" t="n"/>
       <c r="C23" s="58" t="n"/>
       <c r="D23" s="60" t="n"/>
       <c r="E23" s="74" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="82" t="n"/>
+      <c r="A24" s="105" t="n"/>
       <c r="B24" s="61" t="n"/>
       <c r="C24" s="58" t="n"/>
       <c r="D24" s="60" t="n"/>
       <c r="E24" s="74" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="82" t="n"/>
+      <c r="A25" s="105" t="n"/>
       <c r="B25" s="61" t="n"/>
       <c r="C25" s="58" t="n"/>
       <c r="D25" s="60" t="n"/>
       <c r="E25" s="74" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="82" t="n"/>
+      <c r="A26" s="105" t="n"/>
       <c r="B26" s="61" t="n"/>
       <c r="C26" s="58" t="n"/>
       <c r="D26" s="60" t="n"/>
       <c r="E26" s="74" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="82" t="n"/>
+      <c r="A27" s="105" t="n"/>
       <c r="B27" s="61" t="n"/>
       <c r="C27" s="58" t="n"/>
       <c r="D27" s="60" t="n"/>
       <c r="E27" s="74" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="82" t="n"/>
+      <c r="A28" s="105" t="n"/>
       <c r="B28" s="61" t="n"/>
       <c r="C28" s="58" t="n"/>
       <c r="D28" s="60" t="n"/>
       <c r="E28" s="74" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="83" t="n"/>
+      <c r="A29" s="106" t="n"/>
       <c r="B29" s="68" t="n"/>
       <c r="C29" s="65" t="n"/>
       <c r="D29" s="67" t="n"/>
